--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2023_magallanes.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2023_magallanes.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:39</t>
+    <t xml:space="preserve">2026-10-05 02:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>857283.31</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>842713.69</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -778,7 +778,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>845194.12</v>
+        <v>845194.13</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>803301.44</v>
@@ -800,7 +800,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>855153.12</v>
+        <v>855153.13</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>815571.81</v>
@@ -822,7 +822,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>934537.62</v>
+        <v>934537.63</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>876986.31</v>
@@ -836,7 +836,7 @@
         <v>883640.5</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -877,7 +877,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>882290.12</v>
+        <v>882290.13</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>844285.88</v>
@@ -899,7 +899,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>881961.12</v>
+        <v>881961.13</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>852706.38</v>
@@ -913,7 +913,7 @@
         <v>887233.31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -965,7 +965,7 @@
         <v>27</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>923915.62</v>
+        <v>923915.63</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>877882.31</v>
@@ -976,7 +976,7 @@
         <v>28</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>907682.12</v>
+        <v>907682.13</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>865308.75</v>
@@ -1001,7 +1001,7 @@
         <v>919307.19</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>879521.25</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1053,7 +1053,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>959840.12</v>
+        <v>959840.13</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>930460.56</v>
@@ -1086,7 +1086,7 @@
         <v>38</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>990161.62</v>
+        <v>990161.63</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>969716.44</v>
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>954169.12</v>
+        <v>954169.13</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>917146.44</v>
@@ -1166,7 +1166,7 @@
         <v>978895.06</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1174,7 +1174,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>967092.62</v>
+        <v>967092.63</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>941936.56</v>
@@ -1240,7 +1240,7 @@
         <v>52</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1014771.62</v>
+        <v>1014771.63</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>984727.69</v>
@@ -1287,7 +1287,7 @@
         <v>1081920.88</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>1074188.88</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1342,7 +1342,7 @@
         <v>1124965.38</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1350,7 +1350,7 @@
         <v>62</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1221148.62</v>
+        <v>1221148.63</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>1183065.88</v>
@@ -1364,7 +1364,7 @@
         <v>1176485.5</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1419,7 +1419,7 @@
         <v>1219563.88</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1471,7 +1471,7 @@
         <v>73</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>1239118.12</v>
+        <v>1239118.13</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>1219650.75</v>
@@ -1518,7 +1518,7 @@
         <v>1297611.88</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1551,7 +1551,7 @@
         <v>1302843.88</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1283611.5</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1570,7 +1570,7 @@
         <v>82</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>1288725.62</v>
+        <v>1288725.63</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>1271870.5</v>
@@ -1584,7 +1584,7 @@
         <v>1361524.88</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
